--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122021975</v>
+        <v>122021986</v>
       </c>
       <c r="B5" t="n">
         <v>78645</v>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463563</v>
+        <v>463641</v>
       </c>
       <c r="R5" t="n">
-        <v>6391741</v>
+        <v>6391663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122021986</v>
+        <v>122021975</v>
       </c>
       <c r="B6" t="n">
         <v>78645</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463641</v>
+        <v>463563</v>
       </c>
       <c r="R6" t="n">
-        <v>6391663</v>
+        <v>6391741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021979</v>
+        <v>122021988</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>8425</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,40 +1201,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462727</v>
+        <v>462823</v>
       </c>
       <c r="R7" t="n">
-        <v>6391861</v>
+        <v>6391618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,17 +1284,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021989</v>
+        <v>122021983</v>
       </c>
       <c r="B8" t="n">
-        <v>57332</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1307,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102975</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462695</v>
+        <v>462825</v>
       </c>
       <c r="R8" t="n">
-        <v>6391827</v>
+        <v>6391661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,17 +1372,13 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021976</v>
+        <v>122021977</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>8425</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1413,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462765</v>
+        <v>462778</v>
       </c>
       <c r="R9" t="n">
-        <v>6391583</v>
+        <v>6391631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,17 +1492,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021983</v>
+        <v>122021982</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>78734</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,41 +1511,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462825</v>
+        <v>462847</v>
       </c>
       <c r="R10" t="n">
-        <v>6391661</v>
+        <v>6391569</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1583,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1605,17 +1594,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021982</v>
+        <v>122021989</v>
       </c>
       <c r="B11" t="n">
-        <v>78734</v>
+        <v>57332</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,38 +1613,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6450</v>
+        <v>102975</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462847</v>
+        <v>462695</v>
       </c>
       <c r="R11" t="n">
-        <v>6391569</v>
+        <v>6391827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,6 +1683,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1707,14 +1705,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021977</v>
+        <v>122021985</v>
       </c>
       <c r="B12" t="n">
         <v>8425</v>
@@ -1754,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462778</v>
+        <v>462732</v>
       </c>
       <c r="R12" t="n">
-        <v>6391631</v>
+        <v>6391887</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021985</v>
+        <v>122021978</v>
       </c>
       <c r="B13" t="n">
-        <v>8425</v>
+        <v>74686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462732</v>
+        <v>462828</v>
       </c>
       <c r="R13" t="n">
-        <v>6391887</v>
+        <v>6391670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021988</v>
+        <v>122021976</v>
       </c>
       <c r="B14" t="n">
-        <v>8425</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462823</v>
+        <v>462765</v>
       </c>
       <c r="R14" t="n">
-        <v>6391618</v>
+        <v>6391583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,17 +2011,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021978</v>
+        <v>122021979</v>
       </c>
       <c r="B15" t="n">
-        <v>74686</v>
+        <v>78645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,38 +2030,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462828</v>
+        <v>462727</v>
       </c>
       <c r="R15" t="n">
-        <v>6391670</v>
+        <v>6391861</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122021971</v>
+        <v>122021974</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>90754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463241</v>
+        <v>463304</v>
       </c>
       <c r="R2" t="n">
-        <v>6391704</v>
+        <v>6392021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021974</v>
+        <v>122021971</v>
       </c>
       <c r="B4" t="n">
-        <v>90744</v>
+        <v>97139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463304</v>
+        <v>463241</v>
       </c>
       <c r="R4" t="n">
-        <v>6392021</v>
+        <v>6391704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -984,7 +984,7 @@
         <v>122021986</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>122021975</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021988</v>
+        <v>122021989</v>
       </c>
       <c r="B7" t="n">
-        <v>8425</v>
+        <v>57332</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1201,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>102975</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462823</v>
+        <v>462695</v>
       </c>
       <c r="R7" t="n">
-        <v>6391618</v>
+        <v>6391827</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,6 +1271,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1284,17 +1293,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021983</v>
+        <v>122021988</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>8425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,41 +1312,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462825</v>
+        <v>462823</v>
       </c>
       <c r="R8" t="n">
-        <v>6391661</v>
+        <v>6391618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,17 +1395,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021977</v>
+        <v>122021983</v>
       </c>
       <c r="B9" t="n">
-        <v>8425</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,38 +1414,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462778</v>
+        <v>462825</v>
       </c>
       <c r="R9" t="n">
-        <v>6391631</v>
+        <v>6391661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,6 +1489,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1492,17 +1501,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021982</v>
+        <v>122021976</v>
       </c>
       <c r="B10" t="n">
-        <v>78734</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1524,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462847</v>
+        <v>462765</v>
       </c>
       <c r="R10" t="n">
-        <v>6391569</v>
+        <v>6391583</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,17 +1603,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021989</v>
+        <v>122021977</v>
       </c>
       <c r="B11" t="n">
-        <v>57332</v>
+        <v>8425</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,42 +1622,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102975</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462695</v>
+        <v>462778</v>
       </c>
       <c r="R11" t="n">
-        <v>6391827</v>
+        <v>6391631</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,11 +1688,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021985</v>
+        <v>122021982</v>
       </c>
       <c r="B12" t="n">
-        <v>8425</v>
+        <v>78735</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>6450</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462732</v>
+        <v>462847</v>
       </c>
       <c r="R12" t="n">
-        <v>6391887</v>
+        <v>6391569</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021978</v>
+        <v>122021985</v>
       </c>
       <c r="B13" t="n">
-        <v>74686</v>
+        <v>8425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462828</v>
+        <v>462732</v>
       </c>
       <c r="R13" t="n">
-        <v>6391670</v>
+        <v>6391887</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021976</v>
+        <v>122021978</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>74686</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462765</v>
+        <v>462828</v>
       </c>
       <c r="R14" t="n">
-        <v>6391583</v>
+        <v>6391670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
         <v>122021979</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122021974</v>
+        <v>122021973</v>
       </c>
       <c r="B2" t="n">
-        <v>90754</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463304</v>
+        <v>463278</v>
       </c>
       <c r="R2" t="n">
-        <v>6392021</v>
+        <v>6392013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122021973</v>
+        <v>122021971</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463278</v>
+        <v>463241</v>
       </c>
       <c r="R3" t="n">
-        <v>6392013</v>
+        <v>6391704</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021971</v>
+        <v>122021974</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>90754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463241</v>
+        <v>463304</v>
       </c>
       <c r="R4" t="n">
-        <v>6391704</v>
+        <v>6392021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021989</v>
+        <v>122021985</v>
       </c>
       <c r="B7" t="n">
-        <v>57332</v>
+        <v>8425</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,42 +1201,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102975</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462695</v>
+        <v>462732</v>
       </c>
       <c r="R7" t="n">
-        <v>6391827</v>
+        <v>6391887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1267,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1293,17 +1284,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021988</v>
+        <v>122021979</v>
       </c>
       <c r="B8" t="n">
-        <v>8425</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,38 +1303,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462823</v>
+        <v>462727</v>
       </c>
       <c r="R8" t="n">
-        <v>6391618</v>
+        <v>6391861</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,17 +1388,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021983</v>
+        <v>122021977</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>8425</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,41 +1407,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462825</v>
+        <v>462778</v>
       </c>
       <c r="R9" t="n">
-        <v>6391661</v>
+        <v>6391631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1479,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1501,17 +1490,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021976</v>
+        <v>122021983</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1520,38 +1509,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462765</v>
+        <v>462825</v>
       </c>
       <c r="R10" t="n">
-        <v>6391583</v>
+        <v>6391661</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1584,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1603,17 +1596,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021977</v>
+        <v>122021976</v>
       </c>
       <c r="B11" t="n">
-        <v>8425</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462778</v>
+        <v>462765</v>
       </c>
       <c r="R11" t="n">
-        <v>6391631</v>
+        <v>6391583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,17 +1698,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021982</v>
+        <v>122021989</v>
       </c>
       <c r="B12" t="n">
-        <v>78735</v>
+        <v>57332</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,38 +1717,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6450</v>
+        <v>102975</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462847</v>
+        <v>462695</v>
       </c>
       <c r="R12" t="n">
-        <v>6391569</v>
+        <v>6391827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,6 +1787,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1807,14 +1809,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021985</v>
+        <v>122021988</v>
       </c>
       <c r="B13" t="n">
         <v>8425</v>
@@ -1854,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462732</v>
+        <v>462823</v>
       </c>
       <c r="R13" t="n">
-        <v>6391887</v>
+        <v>6391618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021979</v>
+        <v>122021982</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>78735</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,40 +2032,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462727</v>
+        <v>462847</v>
       </c>
       <c r="R15" t="n">
-        <v>6391861</v>
+        <v>6391569</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021979</v>
+        <v>122021977</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>8425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,40 +1303,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462727</v>
+        <v>462778</v>
       </c>
       <c r="R8" t="n">
-        <v>6391861</v>
+        <v>6391631</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,17 +1386,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021977</v>
+        <v>122021979</v>
       </c>
       <c r="B9" t="n">
-        <v>8425</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,38 +1405,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462778</v>
+        <v>462727</v>
       </c>
       <c r="R9" t="n">
-        <v>6391631</v>
+        <v>6391861</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122021973</v>
+        <v>122021971</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463278</v>
+        <v>463241</v>
       </c>
       <c r="R2" t="n">
-        <v>6392013</v>
+        <v>6391704</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122021971</v>
+        <v>122021974</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>90766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463241</v>
+        <v>463304</v>
       </c>
       <c r="R3" t="n">
-        <v>6391704</v>
+        <v>6392021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021974</v>
+        <v>122021973</v>
       </c>
       <c r="B4" t="n">
-        <v>90754</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463304</v>
+        <v>463278</v>
       </c>
       <c r="R4" t="n">
-        <v>6392021</v>
+        <v>6392013</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>122021986</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>122021975</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021985</v>
+        <v>122021976</v>
       </c>
       <c r="B7" t="n">
-        <v>8425</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462732</v>
+        <v>462765</v>
       </c>
       <c r="R7" t="n">
-        <v>6391887</v>
+        <v>6391583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021977</v>
+        <v>122021988</v>
       </c>
       <c r="B8" t="n">
-        <v>8425</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462778</v>
+        <v>462823</v>
       </c>
       <c r="R8" t="n">
-        <v>6391631</v>
+        <v>6391618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021979</v>
+        <v>122021989</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>57337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,36 +1409,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102975</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462727</v>
+        <v>462695</v>
       </c>
       <c r="R9" t="n">
-        <v>6391861</v>
+        <v>6391827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,6 +1473,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021983</v>
+        <v>122021982</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>78740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1509,41 +1516,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462825</v>
+        <v>462847</v>
       </c>
       <c r="R10" t="n">
-        <v>6391661</v>
+        <v>6391569</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,7 +1588,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1596,17 +1599,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021976</v>
+        <v>122021977</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1622,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462765</v>
+        <v>462778</v>
       </c>
       <c r="R11" t="n">
-        <v>6391583</v>
+        <v>6391631</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,17 +1701,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021989</v>
+        <v>122021978</v>
       </c>
       <c r="B12" t="n">
-        <v>57332</v>
+        <v>74691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,42 +1720,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102975</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462695</v>
+        <v>462828</v>
       </c>
       <c r="R12" t="n">
-        <v>6391827</v>
+        <v>6391670</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,11 +1786,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1809,17 +1803,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021988</v>
+        <v>122021979</v>
       </c>
       <c r="B13" t="n">
-        <v>8425</v>
+        <v>78651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,38 +1822,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462823</v>
+        <v>462727</v>
       </c>
       <c r="R13" t="n">
-        <v>6391618</v>
+        <v>6391861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,17 +1907,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021978</v>
+        <v>122021985</v>
       </c>
       <c r="B14" t="n">
-        <v>74686</v>
+        <v>8430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462828</v>
+        <v>462732</v>
       </c>
       <c r="R14" t="n">
-        <v>6391670</v>
+        <v>6391887</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021982</v>
+        <v>122021983</v>
       </c>
       <c r="B15" t="n">
-        <v>78735</v>
+        <v>78651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,38 +2028,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462847</v>
+        <v>462825</v>
       </c>
       <c r="R15" t="n">
-        <v>6391569</v>
+        <v>6391661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,6 +2103,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122021971</v>
+        <v>122021973</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463241</v>
+        <v>463278</v>
       </c>
       <c r="R2" t="n">
-        <v>6391704</v>
+        <v>6392013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>122021974</v>
       </c>
       <c r="B3" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021973</v>
+        <v>122021971</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>97156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463278</v>
+        <v>463241</v>
       </c>
       <c r="R4" t="n">
-        <v>6392013</v>
+        <v>6391704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,14 +974,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122021986</v>
+        <v>122021975</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463641</v>
+        <v>463563</v>
       </c>
       <c r="R5" t="n">
-        <v>6391663</v>
+        <v>6391741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122021975</v>
+        <v>122021986</v>
       </c>
       <c r="B6" t="n">
         <v>78651</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463563</v>
+        <v>463641</v>
       </c>
       <c r="R6" t="n">
-        <v>6391741</v>
+        <v>6391663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021976</v>
+        <v>122021979</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1201,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462765</v>
+        <v>462727</v>
       </c>
       <c r="R7" t="n">
-        <v>6391583</v>
+        <v>6391861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,17 +1286,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021988</v>
+        <v>122021983</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,38 +1305,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462823</v>
+        <v>462825</v>
       </c>
       <c r="R8" t="n">
-        <v>6391618</v>
+        <v>6391661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,6 +1380,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,17 +1392,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021989</v>
+        <v>122021982</v>
       </c>
       <c r="B9" t="n">
-        <v>57337</v>
+        <v>78740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,42 +1411,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102975</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462695</v>
+        <v>462847</v>
       </c>
       <c r="R9" t="n">
-        <v>6391827</v>
+        <v>6391569</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1477,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1497,17 +1494,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021982</v>
+        <v>122021976</v>
       </c>
       <c r="B10" t="n">
-        <v>78740</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1520,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462847</v>
+        <v>462765</v>
       </c>
       <c r="R10" t="n">
-        <v>6391569</v>
+        <v>6391583</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,17 +1596,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021977</v>
+        <v>122021978</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>74691</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462778</v>
+        <v>462828</v>
       </c>
       <c r="R11" t="n">
-        <v>6391631</v>
+        <v>6391670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021978</v>
+        <v>122021977</v>
       </c>
       <c r="B12" t="n">
-        <v>74691</v>
+        <v>8430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1748,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462828</v>
+        <v>462778</v>
       </c>
       <c r="R12" t="n">
-        <v>6391670</v>
+        <v>6391631</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021979</v>
+        <v>122021989</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>57337</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,36 +1823,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102975</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462727</v>
+        <v>462695</v>
       </c>
       <c r="R13" t="n">
-        <v>6391861</v>
+        <v>6391827</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,7 +1918,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021985</v>
+        <v>122021988</v>
       </c>
       <c r="B14" t="n">
         <v>8430</v>
@@ -1954,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462732</v>
+        <v>462823</v>
       </c>
       <c r="R14" t="n">
-        <v>6391887</v>
+        <v>6391618</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021983</v>
+        <v>122021985</v>
       </c>
       <c r="B15" t="n">
-        <v>78651</v>
+        <v>8430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,41 +2032,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462825</v>
+        <v>462732</v>
       </c>
       <c r="R15" t="n">
-        <v>6391661</v>
+        <v>6391887</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2104,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021989</v>
+        <v>122021988</v>
       </c>
       <c r="B13" t="n">
-        <v>57337</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,42 +1819,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102975</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462695</v>
+        <v>462823</v>
       </c>
       <c r="R13" t="n">
-        <v>6391827</v>
+        <v>6391618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,11 +1885,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1911,17 +1902,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021988</v>
+        <v>122021989</v>
       </c>
       <c r="B14" t="n">
-        <v>8430</v>
+        <v>57337</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,38 +1921,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>102975</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462823</v>
+        <v>462695</v>
       </c>
       <c r="R14" t="n">
-        <v>6391618</v>
+        <v>6391827</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,6 +1991,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>106554</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122021974</v>
+        <v>122021971</v>
       </c>
       <c r="B3" t="n">
-        <v>90773</v>
+        <v>97165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463304</v>
+        <v>463241</v>
       </c>
       <c r="R3" t="n">
-        <v>6392021</v>
+        <v>6391704</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021971</v>
+        <v>122021974</v>
       </c>
       <c r="B4" t="n">
-        <v>97156</v>
+        <v>90778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +885,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463241</v>
+        <v>463304</v>
       </c>
       <c r="R4" t="n">
-        <v>6391704</v>
+        <v>6392021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -984,7 +969,7 @@
         <v>122021975</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,11 +983,6 @@
       </c>
       <c r="E5" t="n">
         <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1088,7 +1068,7 @@
         <v>122021986</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1102,11 +1082,6 @@
       </c>
       <c r="E6" t="n">
         <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1189,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021979</v>
+        <v>122021976</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,40 +1176,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462727</v>
+        <v>462765</v>
       </c>
       <c r="R7" t="n">
-        <v>6391861</v>
+        <v>6391583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,17 +1254,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021983</v>
+        <v>122021978</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>74692</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,41 +1273,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6426</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462825</v>
+        <v>462828</v>
       </c>
       <c r="R8" t="n">
-        <v>6391661</v>
+        <v>6391670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,7 +1340,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,17 +1351,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021982</v>
+        <v>122021989</v>
       </c>
       <c r="B9" t="n">
-        <v>78740</v>
+        <v>57337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,38 +1370,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6450</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Skuggblåslav</t>
-        </is>
+        <v>102975</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462847</v>
+        <v>462695</v>
       </c>
       <c r="R9" t="n">
-        <v>6391569</v>
+        <v>6391827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,6 +1435,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1494,17 +1457,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021976</v>
+        <v>122021985</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>8430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1480,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>106554</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462765</v>
+        <v>462732</v>
       </c>
       <c r="R10" t="n">
-        <v>6391583</v>
+        <v>6391887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,17 +1554,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021978</v>
+        <v>122021979</v>
       </c>
       <c r="B11" t="n">
-        <v>74691</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1573,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462828</v>
+        <v>462727</v>
       </c>
       <c r="R11" t="n">
-        <v>6391670</v>
+        <v>6391861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,17 +1653,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021977</v>
+        <v>122021983</v>
       </c>
       <c r="B12" t="n">
-        <v>8430</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,38 +1672,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462778</v>
+        <v>462825</v>
       </c>
       <c r="R12" t="n">
-        <v>6391631</v>
+        <v>6391661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,6 +1742,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1800,17 +1754,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021988</v>
+        <v>122021982</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>78741</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1777,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
+        <v>6450</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462823</v>
+        <v>462847</v>
       </c>
       <c r="R13" t="n">
-        <v>6391618</v>
+        <v>6391569</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021989</v>
+        <v>122021977</v>
       </c>
       <c r="B14" t="n">
-        <v>57337</v>
+        <v>8430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,42 +1870,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102975</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Hornuggla</t>
-        </is>
+        <v>106554</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462695</v>
+        <v>462778</v>
       </c>
       <c r="R14" t="n">
-        <v>6391827</v>
+        <v>6391631</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,11 +1931,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2013,14 +1948,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021985</v>
+        <v>122021988</v>
       </c>
       <c r="B15" t="n">
         <v>8430</v>
@@ -2038,11 +1973,6 @@
       <c r="E15" t="n">
         <v>106554</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
@@ -2060,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462732</v>
+        <v>462823</v>
       </c>
       <c r="R15" t="n">
-        <v>6391887</v>
+        <v>6391618</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>106554</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
@@ -775,7 +780,7 @@
         <v>122021971</v>
       </c>
       <c r="B3" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -872,7 +882,7 @@
         <v>122021974</v>
       </c>
       <c r="B4" t="n">
-        <v>90778</v>
+        <v>90791</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -886,6 +896,11 @@
       </c>
       <c r="E4" t="n">
         <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -969,7 +984,7 @@
         <v>122021975</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -983,6 +998,11 @@
       </c>
       <c r="E5" t="n">
         <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1068,7 +1088,7 @@
         <v>122021986</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1082,6 +1102,11 @@
       </c>
       <c r="E6" t="n">
         <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1164,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021976</v>
+        <v>122021989</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>57341</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1176,33 +1201,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>102975</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462765</v>
+        <v>462695</v>
       </c>
       <c r="R7" t="n">
-        <v>6391583</v>
+        <v>6391827</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,6 +1271,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1254,17 +1293,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021978</v>
+        <v>122021979</v>
       </c>
       <c r="B8" t="n">
-        <v>74692</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1273,33 +1312,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462828</v>
+        <v>462727</v>
       </c>
       <c r="R8" t="n">
-        <v>6391670</v>
+        <v>6391861</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,17 +1397,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021989</v>
+        <v>122021988</v>
       </c>
       <c r="B9" t="n">
-        <v>57337</v>
+        <v>8430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1370,37 +1416,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102975</v>
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462695</v>
+        <v>462823</v>
       </c>
       <c r="R9" t="n">
-        <v>6391827</v>
+        <v>6391618</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1482,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1457,14 +1499,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021985</v>
+        <v>122021977</v>
       </c>
       <c r="B10" t="n">
         <v>8430</v>
@@ -1482,6 +1524,11 @@
       <c r="E10" t="n">
         <v>106554</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Scolytus ratzeburgii</t>
@@ -1499,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462732</v>
+        <v>462778</v>
       </c>
       <c r="R10" t="n">
-        <v>6391887</v>
+        <v>6391631</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021979</v>
+        <v>122021976</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1573,35 +1620,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462727</v>
+        <v>462765</v>
       </c>
       <c r="R11" t="n">
-        <v>6391861</v>
+        <v>6391583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,17 +1703,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021983</v>
+        <v>122021985</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>8430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1672,36 +1722,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462825</v>
+        <v>462732</v>
       </c>
       <c r="R12" t="n">
-        <v>6391661</v>
+        <v>6391887</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1794,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1754,17 +1805,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021982</v>
+        <v>122021983</v>
       </c>
       <c r="B13" t="n">
-        <v>78741</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1773,33 +1824,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462847</v>
+        <v>462825</v>
       </c>
       <c r="R13" t="n">
-        <v>6391569</v>
+        <v>6391661</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,6 +1899,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1851,17 +1911,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021977</v>
+        <v>122021982</v>
       </c>
       <c r="B14" t="n">
-        <v>8430</v>
+        <v>78745</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1874,16 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>6450</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462778</v>
+        <v>462847</v>
       </c>
       <c r="R14" t="n">
-        <v>6391631</v>
+        <v>6391569</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021988</v>
+        <v>122021978</v>
       </c>
       <c r="B15" t="n">
-        <v>8430</v>
+        <v>74696</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1971,16 +2036,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462823</v>
+        <v>462828</v>
       </c>
       <c r="R15" t="n">
-        <v>6391618</v>
+        <v>6391670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122021973</v>
+        <v>122021974</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>90804</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463278</v>
+        <v>463304</v>
       </c>
       <c r="R2" t="n">
-        <v>6392013</v>
+        <v>6392021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>122021971</v>
       </c>
       <c r="B3" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021974</v>
+        <v>122021973</v>
       </c>
       <c r="B4" t="n">
-        <v>90791</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463304</v>
+        <v>463278</v>
       </c>
       <c r="R4" t="n">
-        <v>6392021</v>
+        <v>6392013</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122021975</v>
+        <v>122021986</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463563</v>
+        <v>463641</v>
       </c>
       <c r="R5" t="n">
-        <v>6391741</v>
+        <v>6391663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122021986</v>
+        <v>122021975</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463641</v>
+        <v>463563</v>
       </c>
       <c r="R6" t="n">
-        <v>6391663</v>
+        <v>6391741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021989</v>
+        <v>122021983</v>
       </c>
       <c r="B7" t="n">
-        <v>57341</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,38 +1205,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102975</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462695</v>
+        <v>462825</v>
       </c>
       <c r="R7" t="n">
-        <v>6391827</v>
+        <v>6391661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,17 +1270,13 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1300,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021979</v>
+        <v>122021978</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>74696</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,40 +1307,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462727</v>
+        <v>462828</v>
       </c>
       <c r="R8" t="n">
-        <v>6391861</v>
+        <v>6391670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,14 +1390,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021988</v>
+        <v>122021977</v>
       </c>
       <c r="B9" t="n">
         <v>8430</v>
@@ -1444,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462823</v>
+        <v>462778</v>
       </c>
       <c r="R9" t="n">
-        <v>6391618</v>
+        <v>6391631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021977</v>
+        <v>122021982</v>
       </c>
       <c r="B10" t="n">
-        <v>8430</v>
+        <v>78745</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462778</v>
+        <v>462847</v>
       </c>
       <c r="R10" t="n">
-        <v>6391631</v>
+        <v>6391569</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021976</v>
+        <v>122021988</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462765</v>
+        <v>462823</v>
       </c>
       <c r="R11" t="n">
-        <v>6391583</v>
+        <v>6391618</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,17 +1696,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021985</v>
+        <v>122021976</v>
       </c>
       <c r="B12" t="n">
-        <v>8430</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462732</v>
+        <v>462765</v>
       </c>
       <c r="R12" t="n">
-        <v>6391887</v>
+        <v>6391583</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,17 +1798,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021983</v>
+        <v>122021989</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57341</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,37 +1821,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102975</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462825</v>
+        <v>462695</v>
       </c>
       <c r="R13" t="n">
-        <v>6391661</v>
+        <v>6391827</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,13 +1887,17 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1918,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021982</v>
+        <v>122021985</v>
       </c>
       <c r="B14" t="n">
-        <v>78745</v>
+        <v>8430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6450</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462847</v>
+        <v>462732</v>
       </c>
       <c r="R14" t="n">
-        <v>6391569</v>
+        <v>6391887</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021978</v>
+        <v>122021979</v>
       </c>
       <c r="B15" t="n">
-        <v>74696</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,38 +2030,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462828</v>
+        <v>462727</v>
       </c>
       <c r="R15" t="n">
-        <v>6391670</v>
+        <v>6391861</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122021974</v>
+        <v>122021973</v>
       </c>
       <c r="B2" t="n">
-        <v>90804</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463304</v>
+        <v>463278</v>
       </c>
       <c r="R2" t="n">
-        <v>6392021</v>
+        <v>6392013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021973</v>
+        <v>122021974</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>90804</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463278</v>
+        <v>463304</v>
       </c>
       <c r="R4" t="n">
-        <v>6392013</v>
+        <v>6392021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021983</v>
+        <v>122021982</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78745</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,41 +1201,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462825</v>
+        <v>462847</v>
       </c>
       <c r="R7" t="n">
-        <v>6391661</v>
+        <v>6391569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1273,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,17 +1284,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021978</v>
+        <v>122021985</v>
       </c>
       <c r="B8" t="n">
-        <v>74696</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462828</v>
+        <v>462732</v>
       </c>
       <c r="R8" t="n">
-        <v>6391670</v>
+        <v>6391887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021977</v>
+        <v>122021983</v>
       </c>
       <c r="B9" t="n">
-        <v>8430</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,38 +1405,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462778</v>
+        <v>462825</v>
       </c>
       <c r="R9" t="n">
-        <v>6391631</v>
+        <v>6391661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,6 +1480,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1492,17 +1492,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021982</v>
+        <v>122021977</v>
       </c>
       <c r="B10" t="n">
-        <v>78745</v>
+        <v>8430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462847</v>
+        <v>462778</v>
       </c>
       <c r="R10" t="n">
-        <v>6391569</v>
+        <v>6391631</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021988</v>
+        <v>122021979</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,38 +1613,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462823</v>
+        <v>462727</v>
       </c>
       <c r="R11" t="n">
-        <v>6391618</v>
+        <v>6391861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,17 +1698,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021976</v>
+        <v>122021988</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>8430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462765</v>
+        <v>462823</v>
       </c>
       <c r="R12" t="n">
-        <v>6391583</v>
+        <v>6391618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,17 +1800,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021989</v>
+        <v>122021976</v>
       </c>
       <c r="B13" t="n">
-        <v>57341</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,42 +1819,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102975</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462695</v>
+        <v>462765</v>
       </c>
       <c r="R13" t="n">
-        <v>6391827</v>
+        <v>6391583</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1885,6 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1909,17 +1902,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021985</v>
+        <v>122021978</v>
       </c>
       <c r="B14" t="n">
-        <v>8430</v>
+        <v>74696</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462732</v>
+        <v>462828</v>
       </c>
       <c r="R14" t="n">
-        <v>6391887</v>
+        <v>6391670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021979</v>
+        <v>122021989</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57341</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2034,36 +2027,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102975</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462727</v>
+        <v>462695</v>
       </c>
       <c r="R15" t="n">
-        <v>6391861</v>
+        <v>6391827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,6 +2091,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122021973</v>
+        <v>122021974</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463278</v>
+        <v>463304</v>
       </c>
       <c r="R2" t="n">
-        <v>6392013</v>
+        <v>6392021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,50 +772,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122021971</v>
+        <v>122021975</v>
       </c>
       <c r="B3" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463241</v>
+        <v>463563</v>
       </c>
       <c r="R3" t="n">
-        <v>6391704</v>
+        <v>6391741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,57 +864,54 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122021974</v>
+        <v>122021986</v>
       </c>
       <c r="B4" t="n">
-        <v>90804</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463304</v>
+        <v>463641</v>
       </c>
       <c r="R4" t="n">
-        <v>6392021</v>
+        <v>6391663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,59 +963,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122021986</v>
+        <v>122021973</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463641</v>
+        <v>463278</v>
       </c>
       <c r="R5" t="n">
-        <v>6391663</v>
+        <v>6392013</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,59 +1060,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122021975</v>
+        <v>122021971</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463563</v>
+        <v>463241</v>
       </c>
       <c r="R6" t="n">
-        <v>6391741</v>
+        <v>6391704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,57 +1157,54 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122021982</v>
+        <v>122021979</v>
       </c>
       <c r="B7" t="n">
-        <v>78745</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462847</v>
+        <v>462727</v>
       </c>
       <c r="R7" t="n">
-        <v>6391569</v>
+        <v>6391861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,57 +1256,55 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122021985</v>
+        <v>122021983</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462732</v>
+        <v>462825</v>
       </c>
       <c r="R8" t="n">
-        <v>6391887</v>
+        <v>6391661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,6 +1345,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,22 +1357,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122021983</v>
+        <v>122021978</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,37 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462825</v>
+        <v>462828</v>
       </c>
       <c r="R9" t="n">
-        <v>6391661</v>
+        <v>6391670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,7 +1443,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1492,44 +1454,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122021977</v>
+        <v>122021982</v>
       </c>
       <c r="B10" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>6450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462778</v>
+        <v>462847</v>
       </c>
       <c r="R10" t="n">
-        <v>6391631</v>
+        <v>6391569</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,52 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122021979</v>
+        <v>122021976</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462727</v>
+        <v>462765</v>
       </c>
       <c r="R11" t="n">
-        <v>6391861</v>
+        <v>6391583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,57 +1648,56 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122021988</v>
+        <v>122021989</v>
       </c>
       <c r="B12" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>102975</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462823</v>
+        <v>462695</v>
       </c>
       <c r="R12" t="n">
-        <v>6391618</v>
+        <v>6391827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,11 +1732,16 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1800,22 +1754,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>William Koch</t>
+          <t>William Koch, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122021976</v>
+        <v>122021977</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462765</v>
+        <v>462778</v>
       </c>
       <c r="R13" t="n">
-        <v>6391583</v>
+        <v>6391631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,22 +1851,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122021978</v>
+        <v>122021985</v>
       </c>
       <c r="B14" t="n">
-        <v>74696</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1869,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462828</v>
+        <v>462732</v>
       </c>
       <c r="R14" t="n">
-        <v>6391670</v>
+        <v>6391887</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,54 +1955,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122021989</v>
+        <v>122021988</v>
       </c>
       <c r="B15" t="n">
-        <v>57341</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102975</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tenhult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462695</v>
+        <v>462823</v>
       </c>
       <c r="R15" t="n">
-        <v>6391827</v>
+        <v>6391618</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,16 +2028,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I en ungskog av gran. 3 st i en klunga täta granar. Brunspräckliga, stora (typ korpstorlek, lite mindre kanske men mer bastanta, stora huvuden).</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2115,7 +2045,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>William Koch, Anna Ljungqvist</t>
+          <t>William Koch</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 52402-2024 artfynd.xlsx
+++ b/artfynd/A 52402-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021975</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021986</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021973</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021971</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021979</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021983</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021978</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021982</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021976</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021989</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1855,6 +1915,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021977</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021985</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,8 +2119,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122021988</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>